--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.89849821089781</v>
+        <v>11.0335059592709</v>
       </c>
       <c r="D2" t="n">
-        <v>34.80750637434402</v>
+        <v>5.656219785830904</v>
       </c>
       <c r="E2" t="n">
-        <v>31.64434351665038</v>
+        <v>5.142205821455687</v>
       </c>
       <c r="F2" t="n">
-        <v>11.41239724582061</v>
+        <v>1.854514552445849</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.609811177597056</v>
+        <v>0.7490943163595216</v>
       </c>
       <c r="D3" t="n">
-        <v>57.63230086598524</v>
+        <v>9.365248890722601</v>
       </c>
       <c r="E3" t="n">
-        <v>31.64434351665038</v>
+        <v>5.142205821455687</v>
       </c>
       <c r="F3" t="n">
-        <v>11.41239724582061</v>
+        <v>1.854514552445849</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
